--- a/docs/downloads/04/tbl_other_act_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_ambodivoara.xlsx
@@ -585,12 +585,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/docs/downloads/04/tbl_other_act_alaotra_ambodivoara.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_ambodivoara.xlsx
@@ -384,14 +384,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>90</v>
-      </c>
-      <c r="D2">
-        <v>54.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -402,14 +396,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +414,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +432,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>43</v>
-      </c>
-      <c r="D5">
-        <v>25.9</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -456,14 +444,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -474,32 +462,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C8">
-        <v>827</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>56.4</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="9">
@@ -510,14 +498,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C9">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
@@ -528,14 +516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C10">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D10">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11">
@@ -546,14 +534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C11">
         <v>391</v>
       </c>
       <c r="D11">
-        <v>26.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +552,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C12">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="D12">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="13">
@@ -582,8 +570,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>51</v>
+      </c>
+      <c r="D13">
+        <v>6.9</v>
       </c>
     </row>
     <row r="14">
@@ -594,14 +588,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="D14">
-        <v>0.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="15">
@@ -612,14 +606,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C15">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D15">
-        <v>3.5</v>
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>
